--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithNoneTheme/outputfile.xlsx
@@ -63,6 +63,21 @@
   </x:si>
   <x:si>
     <x:t>SCONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NumberOfOrdersPercentageOfBearclaw</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Row Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(blank)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Total</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -186,9 +201,42 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -1097,7 +1145,90 @@
     <x:col min="2" max="2" width="16.285156" style="0" bestFit="1" customWidth="1"/>
     <x:col min="3" max="3" width="11.140625" style="0" bestFit="1" customWidth="1"/>
   </x:cols>
-  <x:sheetData/>
+  <x:sheetData>
+    <x:row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A1" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C1" s="4"/>
+    </x:row>
+    <x:row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A2" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A3" s="7" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="8">
+        <x:v>1.20814479638009</x:v>
+      </x:c>
+      <x:c r="C3" s="9">
+        <x:v>1.20814479638009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A4" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="11">
+        <x:v>1.54977375565611</x:v>
+      </x:c>
+      <x:c r="C4" s="12">
+        <x:v>1.54977375565611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A5" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="11">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="12">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A6" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B6" s="11">
+        <x:v>1.82126696832579</x:v>
+      </x:c>
+      <x:c r="C6" s="12">
+        <x:v>1.82126696832579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B7" s="11">
+        <x:v>1.70814479638009</x:v>
+      </x:c>
+      <x:c r="C7" s="12">
+        <x:v>1.70814479638009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A8" s="13" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B8" s="14"/>
+      <x:c r="C8" s="15"/>
+    </x:row>
+  </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
